--- a/IMU_CALIBATION_ALL_DATA.xlsx
+++ b/IMU_CALIBATION_ALL_DATA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\UT_CALIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FB21E1-D9E1-45BE-97EC-1D95FCDBF28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD464361-7E43-45A9-90B7-6D379CC46A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6015" yWindow="5460" windowWidth="28755" windowHeight="15435" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
   <si>
     <t>TEST DAY 1</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Success: True  Cost: 3.0194862233818176</t>
+  </si>
+  <si>
+    <t>&amp;GYRO_BIAS GX2.207271GY1.248071GZ0.380602</t>
+  </si>
+  <si>
+    <t>TEST DAY 5</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A04818-9C4B-4D5B-A79D-040ED7377ECE}">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
@@ -1189,6 +1195,26 @@
         <v>90</v>
       </c>
     </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/IMU_CALIBATION_ALL_DATA.xlsx
+++ b/IMU_CALIBATION_ALL_DATA.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\UT_CALIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD464361-7E43-45A9-90B7-6D379CC46A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE43B057-AA22-4D9B-9394-22B253560B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6015" yWindow="5460" windowWidth="28755" windowHeight="15435" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="148">
   <si>
     <t>TEST DAY 1</t>
   </si>
@@ -315,13 +316,178 @@
   </si>
   <si>
     <t>TEST DAY 5</t>
+  </si>
+  <si>
+    <t>DATA  ANALYSIS</t>
+  </si>
+  <si>
+    <t>COMMANDS:</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/manual1.txt</t>
+  </si>
+  <si>
+    <t>Using parameters from reference run on: big_turntable_test_sample.txt</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): -0.003466</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (raw):   0.040090</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.042958</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (raw):   0.252843</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.023015</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (raw):   0.136462</t>
+  </si>
+  <si>
+    <t>Params:</t>
+  </si>
+  <si>
+    <t>7.72898650e-03 -1.31745961e-01 -1.28744674e-01 9.96995134e-01 9.97720064e-01 9.90528954e-01 1.63987347e-03 -2.19314074e-03 -2.21549500e-03</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/manual2.txt</t>
+  </si>
+  <si>
+    <t>1.73797644e-03 -1.37771053e-01 -1.48629030e-01 9.98160419e-01 9.97559960e-01 9.90269011e-01 1.45876946e-03 -3.58944324e-03 8.15213828e-04</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): -0.001355</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.041541</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.019948</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/MANUAL3_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>1.94655176e-02 -1.38498687e-01 -1.77081956e-01 9.96840994e-01 9.97969450e-01 9.92455597e-01 3.84901151e-04 -2.47208826e-03 -1.79370363e-04</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): 0.002781</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.051760</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.022728</t>
+  </si>
+  <si>
+    <t>MANUAL:</t>
+  </si>
+  <si>
+    <t>GUIDED:</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/guided1.txt</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): 0.000408</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.051389</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.025270</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/guided2.txt</t>
+  </si>
+  <si>
+    <t>-3.13593111e-03 -1.43908572e-01 -1.66847034e-01 9.97832917e-01 9.97635081e-01 9.92246167e-01 -3.92565332e-05 -2.15197017e-03 4.87079834e-04</t>
+  </si>
+  <si>
+    <t>-3.53569221e-03 -1.30446830e-01 -1.53933907e-01 9.97342195e-01 9.97334754e-01 9.92096110e-01 7.61337394e-05 -4.16120796e-03 2.98310552e-04</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): 0.003829</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.046917</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.023210</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/guided3.txt</t>
+  </si>
+  <si>
+    <t>-6.17523920e-03 -1.41263564e-01 -1.78929144e-01 9.97568380e-01 9.97678031e-01 9.92155565e-01 3.61831531e-04 -2.46959521e-03 -2.98428350e-04</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): 0.002900</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.055200</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.027670</t>
+  </si>
+  <si>
+    <t>TURNTABLE:</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/TURNTABLE1_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/TURNTABLE2_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>python data_analysis_V3.py --file DATA/big_turntable_test_sample.txt --accel-file DATA/TURNTABLE3_ACCEL.txt</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): -0.001743</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.049929</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.022161</t>
+  </si>
+  <si>
+    <t>3.05352369e-02 -1.30510460e-01 -1.62633195e-01 9.97836533e-01 9.97665618e-01 9.90359965e-01 2.19241644e-03 -3.18093248e-03 2.35448411e-03</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): 0.004049</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.048241</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.019212</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2.59052588e-02 -1.48293908e-01 -1.72857521e-01 9.97493911e-01 9.97486188e-01 9.92835178e-01 2.55881058e-04 -2.63890016e-03 4.96229208e-04</t>
+  </si>
+  <si>
+    <t>Accel: mean offset from g (calib): -0.000923</t>
+  </si>
+  <si>
+    <t>Accel: 95th%% mean abs error (calib): 0.027933</t>
+  </si>
+  <si>
+    <t>Accel: RMS fit to sphere (calib): 0.014047</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,6 +498,14 @@
     <font>
       <sz val="10"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -354,11 +528,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46A04818-9C4B-4D5B-A79D-040ED7377ECE}">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
@@ -1215,6 +1390,431 @@
         <v>23</v>
       </c>
     </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5AA6E1-33C4-4A0B-BFF6-6ACD5AAFA646}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="129.42578125" customWidth="1"/>
+    <col min="2" max="2" width="138.85546875" customWidth="1"/>
+    <col min="3" max="3" width="130" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/IMU_CALIBATION_ALL_DATA.xlsx
+++ b/IMU_CALIBATION_ALL_DATA.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\UT_CALIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE43B057-AA22-4D9B-9394-22B253560B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA5F661-30C8-46B1-87B0-87AB5B96F97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28755" windowHeight="15435" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/IMU_CALIBATION_ALL_DATA.xlsx
+++ b/IMU_CALIBATION_ALL_DATA.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Elu\Reaal\UT\UT_CALIB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA5F661-30C8-46B1-87B0-87AB5B96F97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD0162D-9CBF-4E70-8E00-80DCC5D41807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28755" windowHeight="15435" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{C4B1835E-1845-4776-B4ED-FF7E979FA931}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
